--- a/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -621,7 +621,7 @@
     <t>Specific specialty associated with the agency.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -636,7 +636,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -658,7 +658,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(HealthcareService|4.0.1)
 </t>
   </si>
   <si>
@@ -854,7 +854,7 @@
     <t>PractitionerRole.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>

--- a/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitionerrole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
